--- a/artfynd/A 2985-2025 artfynd.xlsx
+++ b/artfynd/A 2985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,928 @@
           <t>Utter barmarksinventering RMÖ/GDP</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126222245</v>
+      </c>
+      <c r="B3" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>600372</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7304212</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126216824</v>
+      </c>
+      <c r="B4" t="n">
+        <v>77937</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>314</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>600004</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7303405</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126219228</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91596</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600442</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7303692</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126219225</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91254</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600442</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7303692</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126223209</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91254</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>600281</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7303984</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126221475</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>600644</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7304397</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126216827</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75068</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>600004</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7303405</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126217347</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75073</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>599988</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7303528</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126219974</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91254</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>601001</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7303697</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2985-2025 artfynd.xlsx
+++ b/artfynd/A 2985-2025 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>126219228</v>
       </c>
       <c r="B5" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>126219225</v>
       </c>
       <c r="B6" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>126223209</v>
       </c>
       <c r="B7" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>126219974</v>
       </c>
       <c r="B11" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2985-2025 artfynd.xlsx
+++ b/artfynd/A 2985-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126222245</v>
       </c>
       <c r="B3" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>126216824</v>
       </c>
       <c r="B4" t="n">
-        <v>77937</v>
+        <v>77941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126219228</v>
+        <v>126219225</v>
       </c>
       <c r="B5" t="n">
-        <v>91598</v>
+        <v>91260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126219225</v>
+        <v>126219228</v>
       </c>
       <c r="B6" t="n">
-        <v>91256</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
         <v>126223209</v>
       </c>
       <c r="B7" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>126221475</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>126216827</v>
       </c>
       <c r="B9" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>126217347</v>
       </c>
       <c r="B10" t="n">
-        <v>75073</v>
+        <v>75077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>126219974</v>
       </c>
       <c r="B11" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2985-2025 artfynd.xlsx
+++ b/artfynd/A 2985-2025 artfynd.xlsx
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126219225</v>
+        <v>126219228</v>
       </c>
       <c r="B5" t="n">
-        <v>91260</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126219228</v>
+        <v>126219225</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>91260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 2985-2025 artfynd.xlsx
+++ b/artfynd/A 2985-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126222245</v>
       </c>
       <c r="B3" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>126216824</v>
       </c>
       <c r="B4" t="n">
-        <v>77941</v>
+        <v>77944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126219228</v>
+        <v>126219225</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1106,32 +1106,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126219225</v>
+        <v>126219228</v>
       </c>
       <c r="B6" t="n">
-        <v>91260</v>
+        <v>91605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,7 +1211,7 @@
         <v>126223209</v>
       </c>
       <c r="B7" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>126221475</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>126216827</v>
       </c>
       <c r="B9" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>126217347</v>
       </c>
       <c r="B10" t="n">
-        <v>75077</v>
+        <v>75080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>126219974</v>
       </c>
       <c r="B11" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2985-2025 artfynd.xlsx
+++ b/artfynd/A 2985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107168419</v>
+        <v>126216824</v>
       </c>
       <c r="B2" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100077</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergnäs (AC2479), Ly lm</t>
+          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600137.2190454544</v>
+        <v>600004</v>
       </c>
       <c r="R2" t="n">
-        <v>7303542.649466274</v>
+        <v>7303405</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,29 +738,14 @@
           <t>Sorsele</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>AC2479</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,30 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Darius Strasevicius</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Darius Strasevicius</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Utter barmarksinventering RMÖ/GDP</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126222245</v>
       </c>
       <c r="B3" t="n">
-        <v>82792</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126216824</v>
+        <v>126217347</v>
       </c>
       <c r="B4" t="n">
-        <v>77944</v>
+        <v>83312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600004</v>
+        <v>599988</v>
       </c>
       <c r="R4" t="n">
-        <v>7303405</v>
+        <v>7303528</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,32 +985,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126219225</v>
+        <v>126219228</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>92283</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1106,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126219228</v>
+        <v>126221475</v>
       </c>
       <c r="B6" t="n">
-        <v>91605</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600442</v>
+        <v>600644</v>
       </c>
       <c r="R6" t="n">
-        <v>7303692</v>
+        <v>7304397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126223209</v>
+        <v>126216827</v>
       </c>
       <c r="B7" t="n">
-        <v>91263</v>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,21 +1200,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600281</v>
+        <v>600004</v>
       </c>
       <c r="R7" t="n">
-        <v>7303984</v>
+        <v>7303405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,414 +1288,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>126221475</v>
-      </c>
-      <c r="B8" t="n">
-        <v>78980</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>600644</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7304397</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>126216827</v>
-      </c>
-      <c r="B9" t="n">
-        <v>75075</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>600004</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7303405</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>126217347</v>
-      </c>
-      <c r="B10" t="n">
-        <v>75080</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>599988</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7303528</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>126219974</v>
-      </c>
-      <c r="B11" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Abborrbäcken, Abborrbäcken, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>601001</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7303697</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Flerskiktad, och olikåldrig björkskog med inslag av gamla och grova granar, på sentid hårt blädad men sannolikt inte kalavverkad.</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2985-2025 artfynd.xlsx
+++ b/artfynd/A 2985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126216824</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126222245</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126217347</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126219228</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126221475</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,8 +1318,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126216827</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>